--- a/Plot/exposures_meta_analysis_final_combined.xlsx
+++ b/Plot/exposures_meta_analysis_final_combined.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,61 +425,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>number studies</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Pooled RR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>lower CI RR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>upper CI RR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>lower PI RR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>upper PI RR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>I^2 (%)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eggers p-value</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>total N</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>total Cases</t>
         </is>
@@ -563,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4575581064437778</v>
+        <v>0.4575581064437775</v>
       </c>
       <c r="J4" t="n">
         <v>3660</v>
@@ -637,32 +649,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>papaya</t>
+          <t>vitamin_b6</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="E7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.43</v>
+      </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>72.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.006929997867264431</v>
+      </c>
       <c r="J7" t="n">
-        <v>876</v>
+        <v>92079</v>
       </c>
       <c r="K7" t="n">
-        <v>438</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +711,7 @@
         <v>94.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8351773861379138</v>
+        <v>0.8351773861379139</v>
       </c>
       <c r="J8" t="n">
         <v>5809</v>
@@ -705,38 +723,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>vitamin_b6</t>
+          <t>papaya</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="E9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.43</v>
-      </c>
+        <v>0.84</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.006929997867264431</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>92079</v>
+        <v>876</v>
       </c>
       <c r="K9" t="n">
-        <v>3337</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10">
@@ -767,7 +779,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001758518003460142</v>
+        <v>0.001758518003460143</v>
       </c>
       <c r="J10" t="n">
         <v>273560</v>
@@ -841,75 +853,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>omega-3_fatty_acids</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>0.65</v>
       </c>
       <c r="D13" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="F13" t="n">
         <v>0.36</v>
       </c>
       <c r="G13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H13" t="n">
-        <v>79.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="I13" t="n">
-        <v>0.009603755584594278</v>
+        <v>0.5929735955651932</v>
       </c>
       <c r="J13" t="n">
-        <v>1067447</v>
+        <v>242088</v>
       </c>
       <c r="K13" t="n">
-        <v>48416</v>
+        <v>10615</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>omega-3_fatty_acids</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
         <v>0.65</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="E14" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="F14" t="n">
         <v>0.36</v>
       </c>
       <c r="G14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="H14" t="n">
-        <v>68</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5929735955651932</v>
+        <v>0.009603755584594274</v>
       </c>
       <c r="J14" t="n">
-        <v>242088</v>
+        <v>1067447</v>
       </c>
       <c r="K14" t="n">
-        <v>10615</v>
+        <v>48416</v>
       </c>
     </row>
     <row r="15">
@@ -940,7 +952,7 @@
         <v>87.3</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02220092332067387</v>
+        <v>0.02220092332067385</v>
       </c>
       <c r="J15" t="n">
         <v>88794</v>
@@ -952,131 +964,131 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iodine</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>0.68</v>
       </c>
       <c r="D16" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.43</v>
+      </c>
       <c r="H16" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>82.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1176939329825924</v>
+      </c>
       <c r="J16" t="n">
-        <v>3284</v>
+        <v>334206</v>
       </c>
       <c r="K16" t="n">
-        <v>1288</v>
+        <v>132822</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>iodine</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>0.68</v>
       </c>
       <c r="D17" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="E17" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.43</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.1176939329825923</v>
-      </c>
+        <v>44.9</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>334206</v>
+        <v>3284</v>
       </c>
       <c r="K17" t="n">
-        <v>132822</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>oats</t>
+          <t>n-acetylcysteine</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>0.7</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3</v>
+        <v>0.68</v>
       </c>
       <c r="E18" t="n">
-        <v>1.65</v>
+        <v>0.73</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>82.3</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>28604</v>
+        <v>91546</v>
       </c>
       <c r="K18" t="n">
-        <v>1075</v>
+        <v>11901</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>n-acetylcysteine</t>
+          <t>oats</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>0.7</v>
       </c>
       <c r="D19" t="n">
-        <v>0.68</v>
+        <v>0.3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.73</v>
+        <v>1.65</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>82.3</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>91546</v>
+        <v>28604</v>
       </c>
       <c r="K19" t="n">
-        <v>11901</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="20">
@@ -1107,7 +1119,7 @@
         <v>44.2</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1879066502188127</v>
+        <v>0.1879066502188126</v>
       </c>
       <c r="J20" t="n">
         <v>243855</v>
@@ -1119,75 +1131,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>antioxidants</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="D21" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="E21" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H21" t="n">
-        <v>84.2</v>
+        <v>87.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02221627450015601</v>
+        <v>5.466290886526607e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>856523</v>
+        <v>539860</v>
       </c>
       <c r="K21" t="n">
-        <v>267423</v>
+        <v>28634</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>antioxidants</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C22" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="D22" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="F22" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="G22" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="H22" t="n">
-        <v>87</v>
+        <v>84.2</v>
       </c>
       <c r="I22" t="n">
-        <v>2.930546567262836e-05</v>
+        <v>0.022216274500156</v>
       </c>
       <c r="J22" t="n">
-        <v>540284</v>
+        <v>856523</v>
       </c>
       <c r="K22" t="n">
-        <v>28689</v>
+        <v>267423</v>
       </c>
     </row>
     <row r="23">
@@ -1197,34 +1209,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="D23" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="E23" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="F23" t="n">
         <v>0.32</v>
       </c>
       <c r="G23" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="H23" t="n">
-        <v>90.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01919136648399248</v>
+        <v>0.009728933199444161</v>
       </c>
       <c r="J23" t="n">
-        <v>984463</v>
+        <v>982724</v>
       </c>
       <c r="K23" t="n">
-        <v>44792</v>
+        <v>44523</v>
       </c>
     </row>
     <row r="24">
@@ -1286,7 +1298,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.02000889385459848</v>
+        <v>0.02000889385459846</v>
       </c>
       <c r="J25" t="n">
         <v>508427</v>
@@ -1360,7 +1372,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1779303397630421</v>
+        <v>0.177930339763042</v>
       </c>
       <c r="J27" t="n">
         <v>77198</v>
@@ -1397,7 +1409,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09603493939892219</v>
+        <v>0.0960349393989222</v>
       </c>
       <c r="J28" t="n">
         <v>1382343</v>
@@ -1409,69 +1421,63 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cod_liver_oil</t>
+          <t>bcaas</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="D29" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9</v>
+        <v>1.48</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>92.8</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>4001</v>
+        <v>197211</v>
       </c>
       <c r="K29" t="n">
-        <v>1731</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>miso</t>
+          <t>cod_liver_oil</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="E30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G30" t="n">
-        <v>33.61</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>57</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.5607534123225344</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>87065</v>
+        <v>4001</v>
       </c>
       <c r="K30" t="n">
-        <v>751</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="31">
@@ -1502,7 +1508,7 @@
         <v>81</v>
       </c>
       <c r="I31" t="n">
-        <v>0.01389915282783273</v>
+        <v>0.01389915282783272</v>
       </c>
       <c r="J31" t="n">
         <v>248595</v>
@@ -1514,112 +1520,106 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>miso</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="D32" t="n">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="F32" t="n">
-        <v>0.46</v>
+        <v>0.02</v>
       </c>
       <c r="G32" t="n">
-        <v>1.48</v>
+        <v>33.61</v>
       </c>
       <c r="H32" t="n">
-        <v>84.5</v>
+        <v>57</v>
       </c>
       <c r="I32" t="n">
-        <v>0.02877266109333387</v>
+        <v>0.5607534123225345</v>
       </c>
       <c r="J32" t="n">
-        <v>1079462</v>
+        <v>87065</v>
       </c>
       <c r="K32" t="n">
-        <v>52354</v>
+        <v>751</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>non-alcoholic_fermented_foods</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C33" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="D33" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="E33" t="n">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="F33" t="n">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="G33" t="n">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
       <c r="H33" t="n">
-        <v>91.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6522742230222329</v>
+        <v>0.02877266109333387</v>
       </c>
       <c r="J33" t="n">
-        <v>143000</v>
+        <v>1079462</v>
       </c>
       <c r="K33" t="n">
-        <v>41773</v>
+        <v>52354</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fermented_foods</t>
+          <t>flax</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
         <v>0.84</v>
       </c>
       <c r="D34" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="E34" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.1</v>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.006338262199775895</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>1687421</v>
+        <v>6369</v>
       </c>
       <c r="K34" t="n">
-        <v>248942</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="35">
@@ -1681,7 +1681,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>1.784041579231218e-10</v>
+        <v>1.78404157923121e-10</v>
       </c>
       <c r="J36" t="n">
         <v>1597494</v>
@@ -1693,20 +1693,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>flax</t>
+          <t>manganese</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="D37" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="E37" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
@@ -1715,115 +1715,121 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>6369</v>
+        <v>2939</v>
       </c>
       <c r="K37" t="n">
-        <v>2999</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>melatonin</t>
+          <t>yogurt</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="D38" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="H38" t="n">
-        <v>42.3</v>
+        <v>50.4</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9864318175325135</v>
+        <v>0.01216014445622597</v>
       </c>
       <c r="J38" t="n">
-        <v>62422</v>
+        <v>1587902</v>
       </c>
       <c r="K38" t="n">
-        <v>3175</v>
+        <v>244079</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>manganese</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C39" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="D39" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="E39" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+        <v>1.03</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.66</v>
+      </c>
       <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5843314822907089</v>
+      </c>
       <c r="J39" t="n">
-        <v>2939</v>
+        <v>1787554</v>
       </c>
       <c r="K39" t="n">
-        <v>382</v>
+        <v>250200</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yogurt</t>
+          <t>melatonin</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="D40" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="G40" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="H40" t="n">
-        <v>50.4</v>
+        <v>45.5</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01216014445622596</v>
+        <v>0.8096930861186756</v>
       </c>
       <c r="J40" t="n">
-        <v>1587902</v>
+        <v>28894</v>
       </c>
       <c r="K40" t="n">
-        <v>244079</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="41">
@@ -1854,7 +1860,7 @@
         <v>85.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4889561242721969</v>
+        <v>0.4889561242721966</v>
       </c>
       <c r="J41" t="n">
         <v>580493</v>
@@ -1866,75 +1872,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>green_tea</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C42" t="n">
         <v>0.92</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="E42" t="n">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="F42" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="G42" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="H42" t="n">
-        <v>79.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2347657167208256</v>
+        <v>0.004626575242725505</v>
       </c>
       <c r="J42" t="n">
-        <v>235866</v>
+        <v>930114</v>
       </c>
       <c r="K42" t="n">
-        <v>17930</v>
+        <v>77262</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>green_tea</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C43" t="n">
         <v>0.92</v>
       </c>
       <c r="D43" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="G43" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="H43" t="n">
-        <v>76.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.004626575242725492</v>
+        <v>0.2347657167208256</v>
       </c>
       <c r="J43" t="n">
-        <v>930114</v>
+        <v>235866</v>
       </c>
       <c r="K43" t="n">
-        <v>77262</v>
+        <v>17930</v>
       </c>
     </row>
     <row r="44">
@@ -1965,7 +1971,7 @@
         <v>83</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5612991451474088</v>
+        <v>0.5612991451474085</v>
       </c>
       <c r="J44" t="n">
         <v>512782</v>
@@ -2002,7 +2008,7 @@
         <v>83.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9597674472320058</v>
+        <v>0.9597674472320056</v>
       </c>
       <c r="J45" t="n">
         <v>746495</v>
@@ -2076,7 +2082,7 @@
         <v>45.9</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4259906328747252</v>
+        <v>0.4259906328747258</v>
       </c>
       <c r="J47" t="n">
         <v>872194</v>
@@ -2088,199 +2094,199 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bcaas</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
         <v>0.98</v>
       </c>
-      <c r="D48" t="n">
-        <v>0.87</v>
-      </c>
       <c r="E48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G48" t="n">
         <v>1.1</v>
       </c>
-      <c r="F48" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G48" t="n">
-        <v>3.8</v>
-      </c>
       <c r="H48" t="n">
-        <v>85.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2941582730123409</v>
+        <v>0.6133032909092402</v>
       </c>
       <c r="J48" t="n">
-        <v>223922</v>
+        <v>4496801</v>
       </c>
       <c r="K48" t="n">
-        <v>13868</v>
+        <v>406240</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>isoleucine</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="E49" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="F49" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="G49" t="n">
-        <v>1.1</v>
+        <v>1.74</v>
       </c>
       <c r="H49" t="n">
-        <v>88.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6133032909092403</v>
+        <v>0.9376775415524358</v>
       </c>
       <c r="J49" t="n">
-        <v>4496801</v>
+        <v>227916</v>
       </c>
       <c r="K49" t="n">
-        <v>406240</v>
+        <v>15865</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>isoleucine</t>
+          <t>vitamin_k</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="D50" t="n">
-        <v>0.87</v>
+        <v>0.68</v>
       </c>
       <c r="E50" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.74</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.9376775415524358</v>
-      </c>
+        <v>91.8</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>227916</v>
+        <v>5048</v>
       </c>
       <c r="K50" t="n">
-        <v>15865</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>vitamin_k</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C51" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="D51" t="n">
-        <v>0.68</v>
+        <v>0.98</v>
       </c>
       <c r="E51" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+        <v>1.07</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.18</v>
+      </c>
       <c r="H51" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="I51" t="inlineStr"/>
+        <v>90.5</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9812909136692176</v>
+      </c>
       <c r="J51" t="n">
-        <v>5048</v>
+        <v>1887493</v>
       </c>
       <c r="K51" t="n">
-        <v>2592</v>
+        <v>232708</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>conjugated_linoleic_acid</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="D52" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="E52" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="F52" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="G52" t="n">
-        <v>1.18</v>
+        <v>1.82</v>
       </c>
       <c r="H52" t="n">
-        <v>90.5</v>
+        <v>62</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9812909136692176</v>
+        <v>0.4225544208553844</v>
       </c>
       <c r="J52" t="n">
-        <v>1887493</v>
+        <v>380443</v>
       </c>
       <c r="K52" t="n">
-        <v>232708</v>
+        <v>17329</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>quercetin</t>
+          <t>glucosamine</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="D53" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="E53" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
@@ -2289,171 +2295,177 @@
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
-        <v>90630</v>
+        <v>41082</v>
       </c>
       <c r="K53" t="n">
-        <v>710</v>
+        <v>5341</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>conjugated_linoleic_acid</t>
+          <t>leucine</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="D54" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="E54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1.82</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>62</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.4225544208553845</v>
-      </c>
+        <v>40.5</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>380443</v>
+        <v>28476</v>
       </c>
       <c r="K54" t="n">
-        <v>17329</v>
+        <v>5237</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>glucosamine</t>
+          <t>grapefruit</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="D55" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="E55" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>82.8</v>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>41082</v>
+        <v>164504</v>
       </c>
       <c r="K55" t="n">
-        <v>5341</v>
+        <v>5404</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>leucine</t>
+          <t>creatine</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="D56" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="E56" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>40.5</v>
+        <v>0</v>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>28476</v>
+        <v>207</v>
       </c>
       <c r="K56" t="n">
-        <v>5237</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>grapefruit</t>
+          <t>magnesium</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="E57" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+        <v>1.32</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2.19</v>
+      </c>
       <c r="H57" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="I57" t="inlineStr"/>
+        <v>83.8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.9619708795552824</v>
+      </c>
       <c r="J57" t="n">
-        <v>164504</v>
+        <v>1172319</v>
       </c>
       <c r="K57" t="n">
-        <v>5404</v>
+        <v>257639</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>creatine</t>
+          <t>carnitine</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="D58" t="n">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="E58" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+        <v>1.41</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3.02</v>
+      </c>
       <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr"/>
+        <v>82.8</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.7636681889414908</v>
+      </c>
       <c r="J58" t="n">
-        <v>207</v>
+        <v>384266</v>
       </c>
       <c r="K58" t="n">
-        <v>1057</v>
+        <v>140082</v>
       </c>
     </row>
     <row r="59">
@@ -2484,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9877864190999567</v>
+        <v>0.987786419099957</v>
       </c>
       <c r="J59" t="n">
         <v>66508</v>
@@ -2496,341 +2508,335 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>carnitine</t>
+          <t>zinc</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C60" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="E60" t="n">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="F60" t="n">
-        <v>0.42</v>
+        <v>0.16</v>
       </c>
       <c r="G60" t="n">
-        <v>3.02</v>
+        <v>8.09</v>
       </c>
       <c r="H60" t="n">
-        <v>82.8</v>
+        <v>96</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7636681889414909</v>
+        <v>0.6073544042976851</v>
       </c>
       <c r="J60" t="n">
-        <v>384266</v>
+        <v>119440</v>
       </c>
       <c r="K60" t="n">
-        <v>140082</v>
+        <v>10103</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>magnesium</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C61" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="D61" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="E61" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="F61" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="G61" t="n">
-        <v>2.19</v>
+        <v>1.58</v>
       </c>
       <c r="H61" t="n">
-        <v>83.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>0.9619708795552824</v>
+        <v>0.1723925153093609</v>
       </c>
       <c r="J61" t="n">
-        <v>1172319</v>
+        <v>1376214</v>
       </c>
       <c r="K61" t="n">
-        <v>257639</v>
+        <v>221434</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>zinc</t>
+          <t>eggs</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C62" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="D62" t="n">
-        <v>0.68</v>
+        <v>0.95</v>
       </c>
       <c r="E62" t="n">
-        <v>1.91</v>
+        <v>1.39</v>
       </c>
       <c r="F62" t="n">
-        <v>0.16</v>
+        <v>0.67</v>
       </c>
       <c r="G62" t="n">
-        <v>8.09</v>
+        <v>1.96</v>
       </c>
       <c r="H62" t="n">
-        <v>96</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6073544042976849</v>
+        <v>0.7478766568479689</v>
       </c>
       <c r="J62" t="n">
-        <v>119440</v>
+        <v>29487</v>
       </c>
       <c r="K62" t="n">
-        <v>10103</v>
+        <v>5481</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C63" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="D63" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="F63" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H63" t="n">
-        <v>80.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1723925153093609</v>
+        <v>3.550216935243029e-10</v>
       </c>
       <c r="J63" t="n">
-        <v>1376214</v>
+        <v>1188831</v>
       </c>
       <c r="K63" t="n">
-        <v>221434</v>
+        <v>70016</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>phosphorus</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="D64" t="n">
-        <v>0.95</v>
+        <v>0.49</v>
       </c>
       <c r="E64" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1.96</v>
-      </c>
+        <v>3.26</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.7478766568479689</v>
-      </c>
+        <v>78.2</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
-        <v>29487</v>
+        <v>229321</v>
       </c>
       <c r="K64" t="n">
-        <v>5481</v>
+        <v>123051</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>dehydroepiandrosterone</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C65" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="D65" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="E65" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="G65" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="H65" t="n">
-        <v>88.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="I65" t="n">
-        <v>3.550216935243042e-10</v>
+        <v>0.0001090796573211561</v>
       </c>
       <c r="J65" t="n">
-        <v>1188831</v>
+        <v>248188</v>
       </c>
       <c r="K65" t="n">
-        <v>70016</v>
+        <v>127366</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dehydroepiandrosterone</t>
+          <t>glutamine</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="D66" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="E66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1.68</v>
-      </c>
+        <v>1.55</v>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.0001090796573211565</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>248188</v>
+        <v>1024</v>
       </c>
       <c r="K66" t="n">
-        <v>127366</v>
+        <v>417</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>phosphorus</t>
+          <t>cannabidiol</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="D67" t="n">
-        <v>0.49</v>
+        <v>1.39</v>
       </c>
       <c r="E67" t="n">
-        <v>3.26</v>
+        <v>1.4</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>78.2</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>229321</v>
+        <v>124896418350</v>
       </c>
       <c r="K67" t="n">
-        <v>123051</v>
+        <v>51623922</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>glutamine</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="D68" t="n">
-        <v>1.12</v>
+        <v>0.95</v>
       </c>
       <c r="E68" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+        <v>2.31</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G68" t="n">
+        <v>6.92</v>
+      </c>
       <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="inlineStr"/>
+        <v>87.3</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.6033187907654798</v>
+      </c>
       <c r="J68" t="n">
-        <v>1024</v>
+        <v>65169</v>
       </c>
       <c r="K68" t="n">
-        <v>417</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cannabidiol</t>
+          <t>coenzyme_q10</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="D69" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="E69" t="n">
-        <v>1.4</v>
+        <v>2.96</v>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
@@ -2839,108 +2845,40 @@
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>124896418350</v>
+        <v>449</v>
       </c>
       <c r="K69" t="n">
-        <v>51623922</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>pickled_vegetables</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>1.49</v>
+        <v>3.71</v>
       </c>
       <c r="D70" t="n">
-        <v>0.95</v>
+        <v>2.67</v>
       </c>
       <c r="E70" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G70" t="n">
-        <v>6.92</v>
-      </c>
+        <v>4.78</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.60331879076548</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
-        <v>65169</v>
+        <v>718</v>
       </c>
       <c r="K70" t="n">
-        <v>1638</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>coenzyme_q10</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="D71" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E71" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="n">
-        <v>449</v>
-      </c>
-      <c r="K71" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>pickled_vegetables</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="D72" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E72" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="n">
-        <v>718</v>
-      </c>
-      <c r="K72" t="n">
         <v>358</v>
       </c>
     </row>

--- a/Plot/exposures_meta_analysis_final_combined.xlsx
+++ b/Plot/exposures_meta_analysis_final_combined.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,38 +649,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vitamin_b6</t>
+          <t>papaya</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="E7" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.43</v>
-      </c>
+        <v>0.84</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.006929997867264431</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>92079</v>
+        <v>876</v>
       </c>
       <c r="K7" t="n">
-        <v>3337</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8">
@@ -723,32 +717,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>papaya</t>
+          <t>vitamin_b6</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+        <v>0.76</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.43</v>
+      </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>72.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.006929997867264431</v>
+      </c>
       <c r="J9" t="n">
-        <v>876</v>
+        <v>92079</v>
       </c>
       <c r="K9" t="n">
-        <v>438</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="10">
@@ -853,75 +853,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>omega-3_fatty_acids</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>0.65</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="E13" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="F13" t="n">
         <v>0.36</v>
       </c>
       <c r="G13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="H13" t="n">
-        <v>68</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5929735955651932</v>
+        <v>0.009603755584594274</v>
       </c>
       <c r="J13" t="n">
-        <v>242088</v>
+        <v>1067447</v>
       </c>
       <c r="K13" t="n">
-        <v>10615</v>
+        <v>48416</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>omega-3_fatty_acids</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
         <v>0.65</v>
       </c>
       <c r="D14" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="F14" t="n">
         <v>0.36</v>
       </c>
       <c r="G14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H14" t="n">
-        <v>79.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="I14" t="n">
-        <v>0.009603755584594274</v>
+        <v>0.5929735955651932</v>
       </c>
       <c r="J14" t="n">
-        <v>1067447</v>
+        <v>242088</v>
       </c>
       <c r="K14" t="n">
-        <v>48416</v>
+        <v>10615</v>
       </c>
     </row>
     <row r="15">
@@ -964,131 +964,131 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>iodine</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>0.68</v>
       </c>
       <c r="D16" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="E16" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.43</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.1176939329825924</v>
-      </c>
+        <v>44.9</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>334206</v>
+        <v>3284</v>
       </c>
       <c r="K16" t="n">
-        <v>132822</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iodine</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
         <v>0.68</v>
       </c>
       <c r="D17" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.43</v>
+      </c>
       <c r="H17" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>82.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1176939329825924</v>
+      </c>
       <c r="J17" t="n">
-        <v>3284</v>
+        <v>334206</v>
       </c>
       <c r="K17" t="n">
-        <v>1288</v>
+        <v>132822</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>n-acetylcysteine</t>
+          <t>oats</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0.7</v>
       </c>
       <c r="D18" t="n">
-        <v>0.68</v>
+        <v>0.3</v>
       </c>
       <c r="E18" t="n">
-        <v>0.73</v>
+        <v>1.65</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>82.3</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>91546</v>
+        <v>28604</v>
       </c>
       <c r="K18" t="n">
-        <v>11901</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>oats</t>
+          <t>n-acetylcysteine</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>0.7</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3</v>
+        <v>0.68</v>
       </c>
       <c r="E19" t="n">
-        <v>1.65</v>
+        <v>0.73</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>82.3</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>28604</v>
+        <v>91546</v>
       </c>
       <c r="K19" t="n">
-        <v>1075</v>
+        <v>11901</v>
       </c>
     </row>
     <row r="20">
@@ -1273,149 +1273,149 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fish_oil</t>
+          <t>choline</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
         <v>0.76</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="E25" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="F25" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="G25" t="n">
-        <v>2.06</v>
+        <v>4.41</v>
       </c>
       <c r="H25" t="n">
-        <v>82.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="I25" t="n">
-        <v>0.02000889385459846</v>
+        <v>0.1085966579317357</v>
       </c>
       <c r="J25" t="n">
-        <v>508427</v>
+        <v>80262</v>
       </c>
       <c r="K25" t="n">
-        <v>63225</v>
+        <v>6805</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>choline</t>
+          <t>fish_oil</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
         <v>0.76</v>
       </c>
       <c r="D26" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="F26" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="G26" t="n">
-        <v>4.41</v>
+        <v>2.06</v>
       </c>
       <c r="H26" t="n">
-        <v>90.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1085966579317357</v>
+        <v>0.02000889385459846</v>
       </c>
       <c r="J26" t="n">
-        <v>80262</v>
+        <v>508427</v>
       </c>
       <c r="K26" t="n">
-        <v>6805</v>
+        <v>63225</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>betaine</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C27" t="n">
         <v>0.77</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="E27" t="n">
-        <v>1.07</v>
+        <v>0.89</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02</v>
+        <v>0.38</v>
       </c>
       <c r="G27" t="n">
-        <v>37.25</v>
+        <v>1.56</v>
       </c>
       <c r="H27" t="n">
-        <v>81.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.177930339763042</v>
+        <v>0.0960349393989222</v>
       </c>
       <c r="J27" t="n">
-        <v>77198</v>
+        <v>1382343</v>
       </c>
       <c r="K27" t="n">
-        <v>5297</v>
+        <v>76186</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>betaine</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
         <v>0.77</v>
       </c>
       <c r="D28" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>0.89</v>
+        <v>1.07</v>
       </c>
       <c r="F28" t="n">
-        <v>0.38</v>
+        <v>0.02</v>
       </c>
       <c r="G28" t="n">
-        <v>1.56</v>
+        <v>37.25</v>
       </c>
       <c r="H28" t="n">
-        <v>89.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0960349393989222</v>
+        <v>0.177930339763042</v>
       </c>
       <c r="J28" t="n">
-        <v>1382343</v>
+        <v>77198</v>
       </c>
       <c r="K28" t="n">
-        <v>76186</v>
+        <v>5297</v>
       </c>
     </row>
     <row r="29">
@@ -1594,7 +1594,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>flax</t>
+          <t>flaxseed</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1625,7 +1625,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>flaxseed</t>
+          <t>flax</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1724,75 +1724,75 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yogurt</t>
+          <t>fermented_foods</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C38" t="n">
         <v>0.86</v>
       </c>
       <c r="D38" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="G38" t="n">
-        <v>1.08</v>
+        <v>1.66</v>
       </c>
       <c r="H38" t="n">
-        <v>50.4</v>
+        <v>90</v>
       </c>
       <c r="I38" t="n">
-        <v>0.01216014445622597</v>
+        <v>0.5843314822907089</v>
       </c>
       <c r="J38" t="n">
-        <v>1587902</v>
+        <v>1787554</v>
       </c>
       <c r="K38" t="n">
-        <v>244079</v>
+        <v>250200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fermented_foods</t>
+          <t>yogurt</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C39" t="n">
         <v>0.86</v>
       </c>
       <c r="D39" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="E39" t="n">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>0.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>1.66</v>
+        <v>1.08</v>
       </c>
       <c r="H39" t="n">
-        <v>90</v>
+        <v>50.4</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5843314822907089</v>
+        <v>0.01216014445622597</v>
       </c>
       <c r="J39" t="n">
-        <v>1787554</v>
+        <v>1587902</v>
       </c>
       <c r="K39" t="n">
-        <v>250200</v>
+        <v>244079</v>
       </c>
     </row>
     <row r="40">
@@ -1872,75 +1872,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>green_tea</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C42" t="n">
         <v>0.92</v>
       </c>
       <c r="D42" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="G42" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="H42" t="n">
-        <v>76.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>0.004626575242725505</v>
+        <v>0.2347657167208256</v>
       </c>
       <c r="J42" t="n">
-        <v>930114</v>
+        <v>235866</v>
       </c>
       <c r="K42" t="n">
-        <v>77262</v>
+        <v>17930</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>green_tea</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C43" t="n">
         <v>0.92</v>
       </c>
       <c r="D43" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="E43" t="n">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="F43" t="n">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="G43" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="H43" t="n">
-        <v>79.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2347657167208256</v>
+        <v>0.004626575242725505</v>
       </c>
       <c r="J43" t="n">
-        <v>235866</v>
+        <v>930114</v>
       </c>
       <c r="K43" t="n">
-        <v>17930</v>
+        <v>77262</v>
       </c>
     </row>
     <row r="44">
@@ -2236,69 +2236,69 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>conjugated_linoleic_acid</t>
+          <t>glucosamine</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
         <v>1.06</v>
       </c>
       <c r="D52" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="E52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1.82</v>
-      </c>
+        <v>1.21</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>62</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.4225544208553844</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
-        <v>380443</v>
+        <v>41082</v>
       </c>
       <c r="K52" t="n">
-        <v>17329</v>
+        <v>5341</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>glucosamine</t>
+          <t>conjugated_linoleic_acid</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C53" t="n">
         <v>1.06</v>
       </c>
       <c r="D53" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="E53" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+        <v>1.22</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.82</v>
+      </c>
       <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.4225544208553844</v>
+      </c>
       <c r="J53" t="n">
-        <v>41082</v>
+        <v>380443</v>
       </c>
       <c r="K53" t="n">
-        <v>5341</v>
+        <v>17329</v>
       </c>
     </row>
     <row r="54">
@@ -2397,44 +2397,44 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>magnesium</t>
+          <t>chromium</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57" t="n">
         <v>1.13</v>
       </c>
       <c r="D57" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="E57" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="F57" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="G57" t="n">
-        <v>2.19</v>
+        <v>1.74</v>
       </c>
       <c r="H57" t="n">
-        <v>83.8</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9619708795552824</v>
+        <v>0.987786419099957</v>
       </c>
       <c r="J57" t="n">
-        <v>1172319</v>
+        <v>66508</v>
       </c>
       <c r="K57" t="n">
-        <v>257639</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>carnitine</t>
+          <t>magnesium</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2444,65 +2444,65 @@
         <v>1.13</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="E58" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="F58" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="G58" t="n">
-        <v>3.02</v>
+        <v>2.19</v>
       </c>
       <c r="H58" t="n">
-        <v>82.8</v>
+        <v>83.8</v>
       </c>
       <c r="I58" t="n">
-        <v>0.7636681889414908</v>
+        <v>0.9619708795552824</v>
       </c>
       <c r="J58" t="n">
-        <v>384266</v>
+        <v>1172319</v>
       </c>
       <c r="K58" t="n">
-        <v>140082</v>
+        <v>257639</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>chromium</t>
+          <t>carnitine</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" t="n">
         <v>1.13</v>
       </c>
       <c r="D59" t="n">
-        <v>1.06</v>
+        <v>0.9</v>
       </c>
       <c r="E59" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="F59" t="n">
-        <v>0.74</v>
+        <v>0.42</v>
       </c>
       <c r="G59" t="n">
-        <v>1.74</v>
+        <v>3.02</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>82.8</v>
       </c>
       <c r="I59" t="n">
-        <v>0.987786419099957</v>
+        <v>0.7636681889414908</v>
       </c>
       <c r="J59" t="n">
-        <v>66508</v>
+        <v>384266</v>
       </c>
       <c r="K59" t="n">
-        <v>1506</v>
+        <v>140082</v>
       </c>
     </row>
     <row r="60">
@@ -2656,69 +2656,69 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dehydroepiandrosterone</t>
+          <t>phosphorus</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
         <v>1.27</v>
       </c>
       <c r="D64" t="n">
-        <v>1.16</v>
+        <v>0.49</v>
       </c>
       <c r="E64" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1.68</v>
-      </c>
+        <v>3.26</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.0001090796573211561</v>
-      </c>
+        <v>78.2</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
-        <v>248188</v>
+        <v>229321</v>
       </c>
       <c r="K64" t="n">
-        <v>127366</v>
+        <v>123051</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>phosphorus</t>
+          <t>dehydroepiandrosterone</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C65" t="n">
         <v>1.27</v>
       </c>
       <c r="D65" t="n">
-        <v>0.49</v>
+        <v>1.16</v>
       </c>
       <c r="E65" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1.68</v>
+      </c>
       <c r="H65" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="I65" t="inlineStr"/>
+        <v>65.3</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.0001090796573211561</v>
+      </c>
       <c r="J65" t="n">
-        <v>229321</v>
+        <v>248188</v>
       </c>
       <c r="K65" t="n">
-        <v>123051</v>
+        <v>127366</v>
       </c>
     </row>
     <row r="66">
@@ -2786,125 +2786,131 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>203</v>
       </c>
       <c r="C68" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="D68" t="n">
-        <v>0.95</v>
+        <v>1.35</v>
       </c>
       <c r="E68" t="n">
-        <v>2.31</v>
+        <v>1.47</v>
       </c>
       <c r="F68" t="n">
-        <v>0.32</v>
+        <v>0.87</v>
       </c>
       <c r="G68" t="n">
-        <v>6.92</v>
+        <v>2.27</v>
       </c>
       <c r="H68" t="n">
-        <v>87.3</v>
+        <v>98.2</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6033187907654798</v>
+        <v>5.458083868100399e-07</v>
       </c>
       <c r="J68" t="n">
-        <v>65169</v>
+        <v>15632500</v>
       </c>
       <c r="K68" t="n">
-        <v>1638</v>
+        <v>1431754</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>omega-6_fatty_acids</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C69" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="D69" t="n">
-        <v>1.17</v>
+        <v>0.95</v>
       </c>
       <c r="E69" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="F69" t="n">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
       <c r="G69" t="n">
-        <v>5.26</v>
+        <v>6.92</v>
       </c>
       <c r="H69" t="n">
-        <v>50.2</v>
+        <v>87.3</v>
       </c>
       <c r="I69" t="n">
-        <v>0.04297484100725812</v>
+        <v>0.6033187907654798</v>
       </c>
       <c r="J69" t="n">
-        <v>6123</v>
+        <v>65169</v>
       </c>
       <c r="K69" t="n">
-        <v>2981</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>coenzyme_q10</t>
+          <t>omega-6_fatty_acids</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="D70" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="E70" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+        <v>2.2</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5.26</v>
+      </c>
       <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="inlineStr"/>
+        <v>50.2</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.04297484100725812</v>
+      </c>
       <c r="J70" t="n">
-        <v>449</v>
+        <v>6123</v>
       </c>
       <c r="K70" t="n">
-        <v>160</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>pickled_vegetables</t>
+          <t>coenzyme_q10</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>3.71</v>
+        <v>1.94</v>
       </c>
       <c r="D71" t="n">
-        <v>2.67</v>
+        <v>1.19</v>
       </c>
       <c r="E71" t="n">
-        <v>4.78</v>
+        <v>2.96</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
@@ -2913,9 +2919,40 @@
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
+        <v>449</v>
+      </c>
+      <c r="K71" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>pickled_vegetables</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E72" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="n">
         <v>718</v>
       </c>
-      <c r="K71" t="n">
+      <c r="K72" t="n">
         <v>358</v>
       </c>
     </row>

--- a/Plot/exposures_meta_analysis_final_combined.xlsx
+++ b/Plot/exposures_meta_analysis_final_combined.xlsx
@@ -2828,34 +2828,34 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>0.87</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>98.2</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>8.121947612144099e-07</v>
+        <v>5.91216845462099e-07</v>
       </c>
       <c r="J68" s="8" t="n">
-        <v>15616182</v>
+        <v>17027950</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>1431464</v>
+        <v>1688752</v>
       </c>
     </row>
     <row r="69">
